--- a/immunizations/v1.0.0/all-profiles.xlsx
+++ b/immunizations/v1.0.0/all-profiles.xlsx
@@ -3804,7 +3804,7 @@
     <t>http://smart.who.int/immunizations/StructureDefinition/IMMZAdministrativeArea</t>
   </si>
   <si>
-    <t>2026-10-01T12:00:06+00:00</t>
+    <t>2026-10-02T09:40:20+00:00</t>
   </si>
   <si>
     <t>complex-type</t>
